--- a/dataset_t6_grouped/results2/G4/G4_T7861_W0026F0001T0006Z000C1N27_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T7861_W0026F0001T0006Z000C1N27_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>26.75479891820666</v>
+        <v>4.347654824208582</v>
       </c>
       <c r="D2" t="n">
-        <v>26.95811580054371</v>
+        <v>4.380693817588353</v>
       </c>
       <c r="E2" t="n">
-        <v>6.763666120893102</v>
+        <v>1.099095744645129</v>
       </c>
       <c r="F2" t="n">
-        <v>8.791570002275945</v>
+        <v>1.428630125369841</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>22.43510689301624</v>
+        <v>3.645704870115138</v>
       </c>
       <c r="D3" t="n">
-        <v>22.40228259354972</v>
+        <v>3.64037092145183</v>
       </c>
       <c r="E3" t="n">
-        <v>6.763666120893102</v>
+        <v>1.099095744645129</v>
       </c>
       <c r="F3" t="n">
-        <v>8.791570002275945</v>
+        <v>1.428630125369841</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>21.80977505242967</v>
+        <v>3.544088446019822</v>
       </c>
       <c r="D4" t="n">
-        <v>7.793752961965769</v>
+        <v>1.266484856319438</v>
       </c>
       <c r="E4" t="n">
-        <v>6.763666120893102</v>
+        <v>1.099095744645129</v>
       </c>
       <c r="F4" t="n">
-        <v>8.791570002275945</v>
+        <v>1.428630125369841</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>12.48998703521436</v>
+        <v>2.029622893222333</v>
       </c>
       <c r="D5" t="n">
-        <v>10.82647981539112</v>
+        <v>1.759302970001056</v>
       </c>
       <c r="E5" t="n">
-        <v>6.763666120893102</v>
+        <v>1.099095744645129</v>
       </c>
       <c r="F5" t="n">
-        <v>8.791570002275945</v>
+        <v>1.428630125369841</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>32.56064427427005</v>
+        <v>5.291104694568884</v>
       </c>
       <c r="D6" t="n">
-        <v>33.2429989287636</v>
+        <v>5.401987325924085</v>
       </c>
       <c r="E6" t="n">
-        <v>6.763666120893102</v>
+        <v>1.099095744645129</v>
       </c>
       <c r="F6" t="n">
-        <v>8.791570002275945</v>
+        <v>1.428630125369841</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>30.90273486638718</v>
+        <v>5.021694415787916</v>
       </c>
       <c r="D7" t="n">
-        <v>31.53569406244296</v>
+        <v>5.124550285146981</v>
       </c>
       <c r="E7" t="n">
-        <v>6.763666120893102</v>
+        <v>1.099095744645129</v>
       </c>
       <c r="F7" t="n">
-        <v>8.791570002275945</v>
+        <v>1.428630125369841</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>32.35103199917042</v>
+        <v>5.257042699865193</v>
       </c>
       <c r="D8" t="n">
-        <v>31.8308730033081</v>
+        <v>5.172516863037567</v>
       </c>
       <c r="E8" t="n">
-        <v>6.763666120893102</v>
+        <v>1.099095744645129</v>
       </c>
       <c r="F8" t="n">
-        <v>8.791570002275945</v>
+        <v>1.428630125369841</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>22.95930917698123</v>
+        <v>3.73088774125945</v>
       </c>
       <c r="D9" t="n">
-        <v>22.76204758607008</v>
+        <v>3.698832732736388</v>
       </c>
       <c r="E9" t="n">
-        <v>6.763666120893102</v>
+        <v>1.099095744645129</v>
       </c>
       <c r="F9" t="n">
-        <v>8.791570002275945</v>
+        <v>1.428630125369841</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>24.74896578637751</v>
+        <v>4.021706940286346</v>
       </c>
       <c r="D10" t="n">
-        <v>26.40453005504265</v>
+        <v>4.29073613394443</v>
       </c>
       <c r="E10" t="n">
-        <v>6.763666120893102</v>
+        <v>1.099095744645129</v>
       </c>
       <c r="F10" t="n">
-        <v>8.791570002275945</v>
+        <v>1.428630125369841</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>37.30273490270257</v>
+        <v>6.061694421689169</v>
       </c>
       <c r="D11" t="n">
-        <v>35.06113856735018</v>
+        <v>5.697435017194405</v>
       </c>
       <c r="E11" t="n">
-        <v>6.763666120893102</v>
+        <v>1.099095744645129</v>
       </c>
       <c r="F11" t="n">
-        <v>8.791570002275945</v>
+        <v>1.428630125369841</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
